--- a/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 11,65</t>
+          <t>-9,99; 10,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 16,1</t>
+          <t>-6,53; 17,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 17,1</t>
+          <t>-9,05; 16,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,74; -6,93</t>
+          <t>-30,8; -6,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 168,27</t>
+          <t>-53,48; 147,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 184,37</t>
+          <t>-35,88; 190,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 181,07</t>
+          <t>-44,51; 172,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-88,34; -24,64</t>
+          <t>-87,9; -25,73</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 1,56</t>
+          <t>-4,28; 2,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,13</t>
+          <t>-4,23; 3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,43</t>
+          <t>-2,01; 4,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,0</t>
+          <t>-4,8; 1,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,88; 28,99</t>
+          <t>-49,38; 41,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 56,76</t>
+          <t>-36,98; 47,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 85,38</t>
+          <t>-25,15; 85,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,01; 15,79</t>
+          <t>-49,76; 20,3</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 1,77</t>
+          <t>-7,45; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 7,25</t>
+          <t>-3,38; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,26</t>
+          <t>0,24; 9,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 5,87</t>
+          <t>-1,61; 6,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,5; 50,96</t>
+          <t>-75,06; 60,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 258,04</t>
+          <t>-47,47; 267,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 857,7</t>
+          <t>-9,71; 709,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 347,38</t>
+          <t>-44,55; 330,95</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,18</t>
+          <t>-4,12; 1,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,0</t>
+          <t>-1,99; 4,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,42</t>
+          <t>-0,83; 4,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,2</t>
+          <t>-5,01; 0,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 18,0</t>
+          <t>-44,5; 18,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 52,1</t>
+          <t>-18,66; 54,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 81,97</t>
+          <t>-10,93; 86,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 3,54</t>
+          <t>-51,37; 3,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 10,73</t>
+          <t>-10,3; 10,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 17,02</t>
+          <t>-6,09; 15,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 16,01</t>
+          <t>-9,43; 16,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,8; -6,34</t>
+          <t>-33,2; -8,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,48; 147,69</t>
+          <t>-57,89; 139,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 190,8</t>
+          <t>-32,77; 162,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 172,89</t>
+          <t>-45,44; 174,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,9; -25,73</t>
+          <t>-90,68; -30,97</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,2</t>
+          <t>-4,66; 1,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 3,82</t>
+          <t>-3,79; 3,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 4,31</t>
+          <t>-2,44; 4,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,29</t>
+          <t>-5,0; 1,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 41,37</t>
+          <t>-51,1; 28,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 47,53</t>
+          <t>-33,42; 49,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 85,13</t>
+          <t>-28,15; 80,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 20,3</t>
+          <t>-51,67; 19,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,38</t>
+          <t>-7,65; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 7,56</t>
+          <t>-4,03; 6,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 9,02</t>
+          <t>0,38; 9,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 6,08</t>
+          <t>-1,84; 6,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,06; 60,48</t>
+          <t>-77,34; 42,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 267,22</t>
+          <t>-53,29; 214,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 709,99</t>
+          <t>-7,62; 802,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,55; 330,95</t>
+          <t>-49,74; 329,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,23</t>
+          <t>-3,99; 1,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,26</t>
+          <t>-1,8; 4,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,66</t>
+          <t>-0,79; 4,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,2</t>
+          <t>-4,52; 0,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 18,72</t>
+          <t>-43,1; 19,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 54,7</t>
+          <t>-17,64; 56,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 86,24</t>
+          <t>-9,91; 88,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,37; 3,44</t>
+          <t>-47,23; 6,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-18,59</t>
+          <t>-14,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-69,28%</t>
+          <t>-54,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 10,98</t>
+          <t>-9,8; 11,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 15,52</t>
+          <t>-6,07; 16,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 16,34</t>
+          <t>-8,84; 17,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,2; -8,02</t>
+          <t>-27,02; -0,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,89; 139,29</t>
+          <t>-53,85; 168,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 162,56</t>
+          <t>-34,01; 184,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,44; 174,27</t>
+          <t>-46,14; 181,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-90,68; -30,97</t>
+          <t>-80,83; 0,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-21,61%</t>
+          <t>-15,9%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1,67</t>
+          <t>-4,89; 1,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,92</t>
+          <t>-4,17; 4,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 4,09</t>
+          <t>-1,98; 4,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,14</t>
+          <t>-4,41; 1,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 28,44</t>
+          <t>-50,88; 28,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 49,83</t>
+          <t>-34,75; 56,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 80,87</t>
+          <t>-24,62; 85,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 19,39</t>
+          <t>-46,96; 25,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 1,78</t>
+          <t>-7,84; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 6,85</t>
+          <t>-3,04; 7,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 9,1</t>
+          <t>0,55; 9,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,12</t>
+          <t>-0,98; 5,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,34; 42,42</t>
+          <t>-75,5; 50,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 214,94</t>
+          <t>-45,72; 258,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 802,79</t>
+          <t>-0,1; 857,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 329,12</t>
+          <t>-39,78; 369,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-26,7%</t>
+          <t>-18,93%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,22</t>
+          <t>-3,97; 1,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,17</t>
+          <t>-2,11; 4,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,68</t>
+          <t>-0,73; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,38</t>
+          <t>-4,03; 1,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 19,28</t>
+          <t>-42,67; 18,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 56,1</t>
+          <t>-19,37; 52,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 88,26</t>
+          <t>-9,69; 81,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 6,27</t>
+          <t>-42,66; 16,12</t>
         </is>
       </c>
     </row>
